--- a/Experimentation.xlsx
+++ b/Experimentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yashasvitv/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046F41AB-C0D2-1B4B-BBBA-52B472F2A5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A14C9E-5574-7342-BBF2-159A82D21117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16320" firstSheet="3" activeTab="8" xr2:uid="{2335F29A-DB22-4FD1-A07F-74DA6ED9C716}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16320" firstSheet="6" activeTab="8" xr2:uid="{2335F29A-DB22-4FD1-A07F-74DA6ED9C716}"/>
   </bookViews>
   <sheets>
     <sheet name="CVE-2014-016-setup" sheetId="3" r:id="rId1"/>
@@ -805,16 +805,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>121596</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>77955</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>91116</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>88115</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>181427</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>17642</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>150947</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>27802</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -844,8 +844,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4850319" y="7697955"/>
-          <a:ext cx="3437491" cy="1560964"/>
+          <a:off x="3443916" y="6590515"/>
+          <a:ext cx="3412631" cy="1565287"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -866,16 +866,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>263457</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>20267</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>135030</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>77346</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>505555</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>141861</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>377128</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>27704</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -905,8 +905,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="9720904" y="6505373"/>
-          <a:ext cx="5646353" cy="2391382"/>
+          <a:off x="8183120" y="6413076"/>
+          <a:ext cx="5607491" cy="2518898"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -933,60 +933,43 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>70484</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>144779</xdr:rowOff>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>328997</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>24343</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>95460</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B1B25C4-B389-40DB-309D-1C5C08C9EDEA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71061EBE-F2D1-E348-B30A-34B9E16447A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="2508884" y="944879"/>
-          <a:ext cx="8183313" cy="3794761"/>
+          <a:off x="2743200" y="1625600"/>
+          <a:ext cx="9396943" cy="3918160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -996,67 +979,6 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>197500</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8853DD46-4EFF-F851-3837-6C75C60E820B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3048000" y="800100"/>
-          <a:ext cx="7512700" cy="3787140"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1084,7 +1006,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1145,7 +1067,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1179,6 +1101,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>607391</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>110435</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>128839</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>142721</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB07B776-90BD-5D93-7072-187CAC9BC468}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5374492" y="938696"/>
+          <a:ext cx="8374637" cy="4173590"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1186,23 +1152,72 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>137036</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>548934</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{620B1090-5D55-5C71-F409-1041517B1F38}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04686AEB-D02B-4E71-78BC-466B268E9437}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9723120" y="193040"/>
+          <a:ext cx="7589814" cy="3434080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>54701</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>36358</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>10739</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E4492E6-544D-F380-EA34-77679D03CE1C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1225,135 +1240,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1828800" y="480060"/>
-          <a:ext cx="7452236" cy="3756660"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>622548</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>37352</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>319676</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>74704</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FB2D1F0-4ABC-F70A-9E28-64A26A903F93}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="15414313" y="1979705"/>
-          <a:ext cx="7093010" cy="2789019"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>473138</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>87157</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>95404</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E4492E6-544D-F380-EA34-77679D03CE1C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="24304314" y="1780490"/>
-          <a:ext cx="7009902" cy="3170796"/>
+          <a:off x="23287234" y="1507068"/>
+          <a:ext cx="9108724" cy="4261004"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1399,7 +1287,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1460,7 +1348,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1490,6 +1378,50 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>135466</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>84666</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>61371</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F866667-D033-2A30-9494-566F9407B557}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10092266" y="1693334"/>
+          <a:ext cx="11565467" cy="4633370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1814,17 +1746,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{121606B4-6720-4AF1-AD3A-B12F0E9948F7}">
-  <dimension ref="I57:S58"/>
+  <dimension ref="H52:S57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="57" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="52" spans="8:19" x14ac:dyDescent="0.15">
+      <c r="H52" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="8:19" x14ac:dyDescent="0.15">
       <c r="S57" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="58" spans="9:19" x14ac:dyDescent="0.15">
-      <c r="I58" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
